--- a/Scenario Files/HVACRagScenarios.xlsx
+++ b/Scenario Files/HVACRagScenarios.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="P2" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="Q2" t="n">
         <v>0.92</v>
@@ -599,19 +599,19 @@
         <v>0.84</v>
       </c>
       <c r="S2" t="n">
-        <v>0.612</v>
+        <v>0.6575</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>10.19</v>
+        <v>9.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>10.61</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="3">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="Q3" t="n">
         <v>0.83</v>
@@ -680,19 +680,19 @@
         <v>0.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0.617</v>
+        <v>0.6625</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
-        <v>10.04</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="4">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="P4" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.51</v>
@@ -761,19 +761,19 @@
         <v>0.84</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5755</v>
+        <v>0.621</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>9.1</v>
+        <v>8.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>9.470000000000001</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R5" t="n">
         <v>0.61</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5745</v>
+        <v>0.3805</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>8.93</v>
+        <v>12.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7</v>
+        <v>2.46</v>
       </c>
       <c r="W5" t="n">
-        <v>9.109999999999999</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="6">
@@ -911,31 +911,31 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.49</v>
+        <v>0.14</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R6" t="n">
         <v>0.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5855</v>
+        <v>0.3735</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>9.75</v>
+        <v>14.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="W6" t="n">
-        <v>9.94</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="7">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0.61</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.3655</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>10.56</v>
+        <v>15.26</v>
       </c>
       <c r="V7" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="W7" t="n">
-        <v>10.77</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="8">
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="P8" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R8" t="n">
         <v>0.61</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5275000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>10.47</v>
+        <v>15.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="W8" t="n">
-        <v>10.67</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="R9" t="n">
         <v>0.61</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5345000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>11.39</v>
+        <v>16.61</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>3.16</v>
       </c>
       <c r="W9" t="n">
-        <v>11.61</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="10">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R10" t="n">
         <v>0.61</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4815</v>
+        <v>0.2775</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>12.31</v>
+        <v>17.9</v>
       </c>
       <c r="V10" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="W10" t="n">
-        <v>12.54</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="11">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="P11" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="Q11" t="n">
         <v>0.83</v>
@@ -1328,19 +1328,19 @@
         <v>0.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>10.68</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="W11" t="n">
-        <v>10.89</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="12">
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="P12" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>0.92</v>
@@ -1409,19 +1409,19 @@
         <v>0.78</v>
       </c>
       <c r="S12" t="n">
-        <v>0.61</v>
+        <v>0.662</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>10.12</v>
+        <v>9.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="W12" t="n">
-        <v>10.32</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="13">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="P13" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.63</v>
@@ -1490,19 +1490,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5825</v>
+        <v>0.6345</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>9.57</v>
+        <v>8.84</v>
       </c>
       <c r="V13" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>9.75</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="14">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1571,19 +1571,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.611</v>
+        <v>0.6465</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>10.62</v>
+        <v>10.21</v>
       </c>
       <c r="V14" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W14" t="n">
-        <v>10.82</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="15">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="P15" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q15" t="n">
         <v>0.86</v>
@@ -1652,19 +1652,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5960000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>10.24</v>
+        <v>9.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="W15" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="16">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>0.7</v>
@@ -1733,19 +1733,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5834999999999999</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>9.859999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="W16" t="n">
-        <v>10.05</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="P17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R17" t="n">
         <v>0.57</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6495000000000001</v>
+        <v>0.5615</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>6.9</v>
+        <v>9.15</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="W17" t="n">
-        <v>7.03</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="18">
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="P18" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R18" t="n">
         <v>0.57</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6735</v>
+        <v>0.5765</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>7.58</v>
+        <v>9.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="W18" t="n">
-        <v>7.72</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="19">
@@ -1964,31 +1964,31 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0.57</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6585000000000001</v>
+        <v>0.5815</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>8.25</v>
+        <v>10.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="W19" t="n">
-        <v>8.41</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="20">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="P20" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
@@ -2057,19 +2057,19 @@
         <v>0.83</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6689999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>9.26</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>9.44</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="21">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="Q21" t="n">
         <v>0.93</v>
@@ -2138,19 +2138,19 @@
         <v>0.83</v>
       </c>
       <c r="S21" t="n">
-        <v>0.665</v>
+        <v>0.704</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>9.06</v>
+        <v>8.69</v>
       </c>
       <c r="V21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>9.24</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Q22" t="n">
         <v>0.86</v>
@@ -2219,19 +2219,19 @@
         <v>0.83</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6575</v>
+        <v>0.6995</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>8.859999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
-        <v>9.029999999999999</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="23">
@@ -2288,31 +2288,31 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="P23" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R23" t="n">
         <v>0.64</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.4875</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.23</v>
+        <v>11.05</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.37</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="24">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R24" t="n">
         <v>0.64</v>
       </c>
       <c r="S24" t="n">
-        <v>0.632</v>
+        <v>0.4675</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>8.800000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.67</v>
+        <v>2.53</v>
       </c>
       <c r="W24" t="n">
-        <v>8.970000000000001</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="25">
@@ -2450,31 +2450,31 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
       <c r="P25" t="n">
-        <v>0.46</v>
+        <v>0.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="R25" t="n">
         <v>0.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4010000000000001</v>
+        <v>0.2115</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>10.36</v>
+        <v>15.61</v>
       </c>
       <c r="V25" t="n">
-        <v>1.97</v>
+        <v>2.97</v>
       </c>
       <c r="W25" t="n">
-        <v>10.57</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="26">
@@ -2531,31 +2531,31 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="P26" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="R26" t="n">
         <v>0.67</v>
       </c>
       <c r="S26" t="n">
-        <v>0.889</v>
+        <v>0.8295</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>3.49</v>
+        <v>5.55</v>
       </c>
       <c r="V26" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>3.41</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="27">
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R27" t="n">
         <v>0.67</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8335</v>
+        <v>0.781</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.93</v>
+        <v>4.72</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W27" t="n">
-        <v>2.86</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="28">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2705,19 +2705,19 @@
         <v>0.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6625</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.37</v>
+        <v>3.89</v>
       </c>
       <c r="V28" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="W28" t="n">
-        <v>2.31</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="29">
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="P29" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R29" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8140000000000001</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>3.54</v>
+        <v>5.49</v>
       </c>
       <c r="V29" t="n">
-        <v>0.67</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>3.46</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="30">
@@ -2855,31 +2855,31 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R30" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8510000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>3.87</v>
+        <v>5.97</v>
       </c>
       <c r="V30" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
-        <v>3.77</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="31">
@@ -2936,31 +2936,31 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="P31" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="R31" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>0.866</v>
+        <v>0.797</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>4.08</v>
+        <v>6.29</v>
       </c>
       <c r="V31" t="n">
-        <v>0.78</v>
+        <v>1.2</v>
       </c>
       <c r="W31" t="n">
-        <v>3.98</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="32">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="Q32" t="n">
         <v>0.78</v>
@@ -3029,19 +3029,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8655</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>5.04</v>
+        <v>4.81</v>
       </c>
       <c r="V32" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="W32" t="n">
-        <v>5.14</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="33">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="P33" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
@@ -3110,19 +3110,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8665</v>
+        <v>0.912</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4.68</v>
+        <v>4.45</v>
       </c>
       <c r="V33" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="W33" t="n">
-        <v>4.77</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="34">
@@ -3179,31 +3179,31 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8949999999999999</v>
+        <v>0.879</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="35">
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q35" t="n">
         <v>0.45</v>
@@ -3272,19 +3272,19 @@
         <v>0.67</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1905</v>
+        <v>0.1975</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>17.79</v>
+        <v>17.25</v>
       </c>
       <c r="V35" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="W35" t="n">
-        <v>18.14</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="36">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="P36" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3353,19 +3353,19 @@
         <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>0.418</v>
+        <v>0.444</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>15.18</v>
+        <v>14.64</v>
       </c>
       <c r="V36" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="W36" t="n">
-        <v>15.48</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="37">
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="P37" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="Q37" t="n">
         <v>0.76</v>
@@ -3434,19 +3434,19 @@
         <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>0.422</v>
+        <v>0.4575</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>13.88</v>
+        <v>13.33</v>
       </c>
       <c r="V37" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="W37" t="n">
-        <v>14.14</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="38">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="P38" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="Q38" t="n">
         <v>0.78</v>
@@ -3515,19 +3515,19 @@
         <v>0.85</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7349999999999999</v>
+        <v>0.7805</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>6.59</v>
+        <v>6.41</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
-        <v>6.86</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="39">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0.93</v>
@@ -3596,19 +3596,19 @@
         <v>0.85</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7845</v>
+        <v>0.8265</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>6.17</v>
+        <v>5.98</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>6.42</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="40">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="P40" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="Q40" t="n">
         <v>0.51</v>
@@ -3677,19 +3677,19 @@
         <v>0.85</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7235</v>
+        <v>0.7655</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>5.64</v>
+        <v>5.45</v>
       </c>
       <c r="V40" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>5.87</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="41">
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="P41" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R41" t="n">
         <v>0.63</v>
       </c>
       <c r="S41" t="n">
-        <v>0.5995</v>
+        <v>0.4205</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>7.89</v>
+        <v>12.02</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="W41" t="n">
-        <v>8.050000000000001</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="42">
@@ -3827,31 +3827,31 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.55</v>
+        <v>0.26</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R42" t="n">
         <v>0.63</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>8.84</v>
+        <v>13.39</v>
       </c>
       <c r="V42" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="W42" t="n">
-        <v>9.01</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="43">
@@ -3908,31 +3908,31 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="P43" t="n">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="R43" t="n">
         <v>0.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0.537</v>
+        <v>0.327</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>10.25</v>
+        <v>15.44</v>
       </c>
       <c r="V43" t="n">
-        <v>1.95</v>
+        <v>2.93</v>
       </c>
       <c r="W43" t="n">
-        <v>10.45</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="44">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="P44" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="Q44" t="n">
         <v>0.78</v>
@@ -4001,19 +4001,19 @@
         <v>0.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0.677</v>
+        <v>0.719</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>8.09</v>
+        <v>7.74</v>
       </c>
       <c r="V44" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W44" t="n">
-        <v>8.25</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="45">
@@ -4070,31 +4070,31 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="Q45" t="n">
         <v>0.93</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="S45" t="n">
-        <v>0.956</v>
+        <v>0.788</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="46">
@@ -4151,31 +4151,31 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8829999999999999</v>
+        <v>0.768</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="47">
@@ -4232,31 +4232,31 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R47" t="n">
         <v>0.72</v>
       </c>
       <c r="S47" t="n">
-        <v>0.8504999999999999</v>
+        <v>0.8175</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>2.6</v>
+        <v>3.98</v>
       </c>
       <c r="V47" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="W47" t="n">
-        <v>2.71</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="48">
@@ -4313,31 +4313,31 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="P48" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R48" t="n">
         <v>0.72</v>
       </c>
       <c r="S48" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>3.29</v>
+        <v>4.96</v>
       </c>
       <c r="V48" t="n">
-        <v>0.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W48" t="n">
-        <v>3.43</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="49">
@@ -4394,31 +4394,31 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="P49" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>0.72</v>
       </c>
       <c r="S49" t="n">
-        <v>0.8560000000000001</v>
+        <v>0.8245</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>3.99</v>
+        <v>5.94</v>
       </c>
       <c r="V49" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="W49" t="n">
-        <v>4.15</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="50">
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="P50" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="R50" t="n">
         <v>0.6</v>
       </c>
       <c r="S50" t="n">
-        <v>0.611</v>
+        <v>0.457</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>7.03</v>
+        <v>10.58</v>
       </c>
       <c r="V50" t="n">
-        <v>1.34</v>
+        <v>2.01</v>
       </c>
       <c r="W50" t="n">
-        <v>7.17</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="51">
@@ -4556,31 +4556,31 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="P51" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R51" t="n">
         <v>0.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0.662</v>
+        <v>0.4965</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>7.93</v>
+        <v>11.88</v>
       </c>
       <c r="V51" t="n">
-        <v>1.51</v>
+        <v>2.26</v>
       </c>
       <c r="W51" t="n">
-        <v>8.08</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="52">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.53</v>
+        <v>0.22</v>
       </c>
       <c r="P52" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="R52" t="n">
         <v>0.6</v>
       </c>
       <c r="S52" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>9.18</v>
+        <v>13.71</v>
       </c>
       <c r="V52" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="W52" t="n">
-        <v>9.359999999999999</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="53">
@@ -4718,31 +4718,31 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0.72</v>
       </c>
       <c r="S53" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.4825</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>5.87</v>
+        <v>9.33</v>
       </c>
       <c r="V53" t="n">
-        <v>1.12</v>
+        <v>1.77</v>
       </c>
       <c r="W53" t="n">
-        <v>5.73</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="P54" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="R54" t="n">
         <v>0.72</v>
       </c>
       <c r="S54" t="n">
-        <v>0.701</v>
+        <v>0.5455</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>6.31</v>
+        <v>9.98</v>
       </c>
       <c r="V54" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="W54" t="n">
-        <v>6.16</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="55">
@@ -4880,31 +4880,31 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="P55" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R55" t="n">
         <v>0.72</v>
       </c>
       <c r="S55" t="n">
-        <v>0.7454999999999999</v>
+        <v>0.5895</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>6.75</v>
+        <v>10.62</v>
       </c>
       <c r="V55" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="W55" t="n">
-        <v>6.59</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="56">
@@ -4967,13 +4967,13 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="R56" t="n">
         <v>0.78</v>
       </c>
       <c r="S56" t="n">
-        <v>0.825</v>
+        <v>0.797</v>
       </c>
       <c r="T56" t="n">
         <v>3</v>
@@ -5048,13 +5048,13 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R57" t="n">
         <v>0.91</v>
       </c>
       <c r="S57" t="n">
-        <v>0.9264999999999999</v>
+        <v>0.9085</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -5129,25 +5129,25 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="R58" t="n">
         <v>0.91</v>
       </c>
       <c r="S58" t="n">
-        <v>0.9724999999999999</v>
+        <v>0.9585</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="59">
@@ -5210,25 +5210,25 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R59" t="n">
         <v>0.82</v>
       </c>
       <c r="S59" t="n">
-        <v>0.8949999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>0.62</v>
+        <v>1.45</v>
       </c>
       <c r="V59" t="n">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="W59" t="n">
-        <v>0.64</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="60">
@@ -5291,25 +5291,25 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R60" t="n">
         <v>0.82</v>
       </c>
       <c r="S60" t="n">
-        <v>0.945</v>
+        <v>0.929</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>1.67</v>
+        <v>2.93</v>
       </c>
       <c r="V60" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W60" t="n">
-        <v>1.7</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="61">
@@ -5366,31 +5366,31 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="R61" t="n">
         <v>0.82</v>
       </c>
       <c r="S61" t="n">
-        <v>0.9564999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>2.37</v>
+        <v>3.91</v>
       </c>
       <c r="V61" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="W61" t="n">
-        <v>2.42</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62">
@@ -5453,16 +5453,16 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R62" t="n">
         <v>0.91</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9584999999999999</v>
+        <v>0.9425</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5534,16 +5534,16 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R63" t="n">
         <v>0.87</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9524999999999999</v>
+        <v>0.9665</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5615,13 +5615,13 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="R64" t="n">
         <v>0.87</v>
       </c>
       <c r="S64" t="n">
-        <v>0.8824999999999998</v>
+        <v>0.9025</v>
       </c>
       <c r="T64" t="n">
         <v>3</v>
@@ -5696,13 +5696,13 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R65" t="n">
         <v>0.87</v>
       </c>
       <c r="S65" t="n">
-        <v>0.8824999999999998</v>
+        <v>0.8625</v>
       </c>
       <c r="T65" t="n">
         <v>3</v>
@@ -5777,16 +5777,16 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R66" t="n">
         <v>0.87</v>
       </c>
       <c r="S66" t="n">
-        <v>0.9524999999999999</v>
+        <v>0.9365</v>
       </c>
       <c r="T66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -5858,25 +5858,25 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R67" t="n">
         <v>0.84</v>
       </c>
       <c r="S67" t="n">
-        <v>0.948</v>
+        <v>0.962</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5933,31 +5933,31 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="P68" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="R68" t="n">
         <v>0.64</v>
       </c>
       <c r="S68" t="n">
-        <v>0.718</v>
+        <v>0.639</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>6.69</v>
+        <v>6.14</v>
       </c>
       <c r="V68" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="W68" t="n">
-        <v>6.82</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="69">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="R69" t="n">
         <v>0.85</v>
       </c>
       <c r="S69" t="n">
-        <v>0.9475</v>
+        <v>0.8105</v>
       </c>
       <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="70">
@@ -6095,31 +6095,31 @@
         </is>
       </c>
       <c r="O70" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q70" t="n">
         <v>1</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0.45</v>
       </c>
       <c r="R70" t="n">
         <v>0.85</v>
       </c>
       <c r="S70" t="n">
-        <v>0.8674999999999999</v>
+        <v>0.9155</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="71">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="P71" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -6188,19 +6188,19 @@
         <v>0.89</v>
       </c>
       <c r="S71" t="n">
-        <v>0.847</v>
+        <v>0.8955</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>5.17</v>
+        <v>4.88</v>
       </c>
       <c r="V71" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="W71" t="n">
-        <v>5.38</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="72">
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="P72" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="Q72" t="n">
         <v>0.7</v>
@@ -6269,19 +6269,19 @@
         <v>0.89</v>
       </c>
       <c r="S72" t="n">
-        <v>0.8065</v>
+        <v>0.8615</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>4.69</v>
+        <v>4.39</v>
       </c>
       <c r="V72" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="W72" t="n">
-        <v>4.88</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="73">
@@ -6338,31 +6338,31 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="Q73" t="n">
         <v>0.41</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="S73" t="n">
-        <v>0.7979999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="74">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P74" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q74" t="n">
         <v>0.86</v>
@@ -6431,19 +6431,19 @@
         <v>0.86</v>
       </c>
       <c r="S74" t="n">
-        <v>0.8665</v>
+        <v>0.912</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>4.02</v>
+        <v>3.89</v>
       </c>
       <c r="V74" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="W74" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="75">
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="P75" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="Q75" t="n">
         <v>0.93</v>
@@ -6512,19 +6512,19 @@
         <v>0.86</v>
       </c>
       <c r="S75" t="n">
-        <v>0.8935000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="V75" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="W75" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="76">
@@ -6584,28 +6584,28 @@
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="Q76" t="n">
         <v>0.61</v>
       </c>
       <c r="R76" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8559999999999999</v>
+        <v>0.8975</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="77">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="P77" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q77" t="n">
         <v>0.92</v>
@@ -6674,19 +6674,19 @@
         <v>0.9</v>
       </c>
       <c r="S77" t="n">
-        <v>0.7120000000000001</v>
+        <v>0.7575</v>
       </c>
       <c r="T77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>8.050000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="V77" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W77" t="n">
-        <v>8.380000000000001</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="78">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="P78" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="Q78" t="n">
         <v>0.51</v>
@@ -6755,19 +6755,19 @@
         <v>0.9</v>
       </c>
       <c r="S78" t="n">
-        <v>0.6625</v>
+        <v>0.7145</v>
       </c>
       <c r="T78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
-        <v>7.24</v>
+        <v>6.82</v>
       </c>
       <c r="V78" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W78" t="n">
-        <v>7.54</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="79">
@@ -6824,31 +6824,31 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="P79" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="Q79" t="n">
         <v>0.06</v>
       </c>
       <c r="R79" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="S79" t="n">
-        <v>0.716</v>
+        <v>0.616</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="80">
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="P80" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="Q80" t="n">
         <v>0.86</v>
@@ -6917,19 +6917,19 @@
         <v>0.77</v>
       </c>
       <c r="S80" t="n">
-        <v>0.7945</v>
+        <v>0.843</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="W80" t="n">
         <v>5.33</v>
-      </c>
-      <c r="V80" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W80" t="n">
-        <v>5.55</v>
       </c>
     </row>
     <row r="81">
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="P81" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="Q81" t="n">
         <v>0.61</v>
@@ -6998,19 +6998,19 @@
         <v>0.84</v>
       </c>
       <c r="S81" t="n">
-        <v>0.7645</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>5.07</v>
+        <v>4.86</v>
       </c>
       <c r="V81" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="W81" t="n">
-        <v>5.27</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="82">
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="P82" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="Q82" t="n">
         <v>0.29</v>
@@ -7079,19 +7079,19 @@
         <v>0.63</v>
       </c>
       <c r="S82" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.7275</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
       </c>
       <c r="U82" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="V82" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="W82" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="83">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="P83" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7160,19 +7160,19 @@
         <v>0.29</v>
       </c>
       <c r="S83" t="n">
-        <v>0.573</v>
+        <v>0.495</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>4.81</v>
+        <v>7.27</v>
       </c>
       <c r="V83" t="n">
-        <v>0.91</v>
+        <v>1.38</v>
       </c>
       <c r="W83" t="n">
-        <v>5.01</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="84">
@@ -7229,31 +7229,31 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="P84" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="R84" t="n">
         <v>0.62</v>
       </c>
       <c r="S84" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.5765</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>5.28</v>
+        <v>7.95</v>
       </c>
       <c r="V84" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="W84" t="n">
-        <v>5.5</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -7310,31 +7310,31 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="P85" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R85" t="n">
         <v>0.62</v>
       </c>
       <c r="S85" t="n">
-        <v>0.7204999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>5.75</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="V85" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="W85" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="86">
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="P86" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="Q86" t="n">
         <v>0.78</v>
@@ -7403,19 +7403,19 @@
         <v>0.84</v>
       </c>
       <c r="S86" t="n">
-        <v>0.6755</v>
+        <v>0.7175</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>8.1</v>
+        <v>7.73</v>
       </c>
       <c r="V86" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W86" t="n">
-        <v>8.26</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="87">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="P87" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -7484,19 +7484,19 @@
         <v>0.84</v>
       </c>
       <c r="S87" t="n">
-        <v>0.739</v>
+        <v>0.781</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>7.68</v>
+        <v>7.31</v>
       </c>
       <c r="V87" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W87" t="n">
-        <v>7.82</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="88">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="P88" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="Q88" t="n">
         <v>0.78</v>
@@ -7565,19 +7565,19 @@
         <v>0.88</v>
       </c>
       <c r="S88" t="n">
-        <v>0.717</v>
+        <v>0.7625</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>7.25</v>
+        <v>6.88</v>
       </c>
       <c r="V88" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W88" t="n">
-        <v>7.39</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="89">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="P89" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0.29</v>
       </c>
       <c r="S89" t="n">
-        <v>0.596</v>
+        <v>0.5435</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>4.23</v>
+        <v>6.27</v>
       </c>
       <c r="V89" t="n">
-        <v>0.8</v>
+        <v>1.19</v>
       </c>
       <c r="W89" t="n">
-        <v>4.4</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="90">
@@ -7715,31 +7715,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="P90" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="R90" t="n">
         <v>0.61</v>
       </c>
       <c r="S90" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>4.71</v>
+        <v>6.96</v>
       </c>
       <c r="V90" t="n">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="W90" t="n">
-        <v>4.91</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="91">
@@ -7796,31 +7796,31 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="P91" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R91" t="n">
         <v>0.61</v>
       </c>
       <c r="S91" t="n">
-        <v>0.745</v>
+        <v>0.652</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>5.2</v>
+        <v>7.65</v>
       </c>
       <c r="V91" t="n">
-        <v>0.99</v>
+        <v>1.45</v>
       </c>
       <c r="W91" t="n">
-        <v>5.42</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="92">
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="P92" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
@@ -7889,19 +7889,19 @@
         <v>0.8</v>
       </c>
       <c r="S92" t="n">
-        <v>0.535</v>
+        <v>0.5705</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>12.34</v>
+        <v>11.83</v>
       </c>
       <c r="V92" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="W92" t="n">
-        <v>12.58</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="93">
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="P93" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Q93" t="n">
         <v>0.76</v>
@@ -7970,19 +7970,19 @@
         <v>0.8</v>
       </c>
       <c r="S93" t="n">
-        <v>0.5225</v>
+        <v>0.5615</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>11.53</v>
+        <v>11.02</v>
       </c>
       <c r="V93" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="W93" t="n">
-        <v>11.75</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="94">
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="P94" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Q94" t="n">
         <v>0.45</v>
@@ -8051,19 +8051,19 @@
         <v>0.8</v>
       </c>
       <c r="S94" t="n">
-        <v>0.493</v>
+        <v>0.535</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
       </c>
       <c r="U94" t="n">
-        <v>10.72</v>
+        <v>10.2</v>
       </c>
       <c r="V94" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="W94" t="n">
-        <v>10.93</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="95">
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="P95" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8132,19 +8132,19 @@
         <v>0.25</v>
       </c>
       <c r="S95" t="n">
-        <v>0.447</v>
+        <v>0.369</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>7.59</v>
+        <v>9.9</v>
       </c>
       <c r="V95" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="W95" t="n">
-        <v>7.9</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="96">
@@ -8201,31 +8201,31 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="P96" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R96" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>8.449999999999999</v>
+        <v>10.96</v>
       </c>
       <c r="V96" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="W96" t="n">
-        <v>8.789999999999999</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="97">
@@ -8282,31 +8282,31 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.52</v>
+        <v>0.2</v>
       </c>
       <c r="P97" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R97" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>0.594</v>
+        <v>0.426</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>9.300000000000001</v>
+        <v>12.01</v>
       </c>
       <c r="V97" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="W97" t="n">
-        <v>9.68</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="98">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="Q98" t="n">
         <v>0.7</v>
@@ -8375,19 +8375,19 @@
         <v>0.78</v>
       </c>
       <c r="S98" t="n">
-        <v>0.638</v>
+        <v>0.677</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>8.66</v>
+        <v>8.35</v>
       </c>
       <c r="V98" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W98" t="n">
-        <v>8.449999999999999</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="99">
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="P99" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q99" t="n">
         <v>0.93</v>
@@ -8456,19 +8456,19 @@
         <v>0.78</v>
       </c>
       <c r="S99" t="n">
-        <v>0.7035</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
       </c>
       <c r="U99" t="n">
-        <v>8.08</v>
+        <v>7.78</v>
       </c>
       <c r="V99" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W99" t="n">
-        <v>7.89</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="100">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="P100" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q100" t="n">
         <v>0.86</v>
@@ -8537,19 +8537,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S100" t="n">
-        <v>0.72</v>
+        <v>0.762</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>7.51</v>
+        <v>7.21</v>
       </c>
       <c r="V100" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W100" t="n">
-        <v>7.33</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="101">
@@ -8606,31 +8606,31 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="P101" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R101" t="n">
         <v>0.78</v>
       </c>
       <c r="S101" t="n">
-        <v>0.8494999999999999</v>
+        <v>0.8165</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="V101" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="W101" t="n">
-        <v>2.37</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="102">
@@ -8687,31 +8687,31 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="P102" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="R102" t="n">
         <v>0.78</v>
       </c>
       <c r="S102" t="n">
-        <v>0.8905</v>
+        <v>0.8485</v>
       </c>
       <c r="T102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>2.83</v>
+        <v>4.44</v>
       </c>
       <c r="V102" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="W102" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="103">
@@ -8768,31 +8768,31 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="P103" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0.93</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1</v>
       </c>
       <c r="R103" t="n">
         <v>0.66</v>
       </c>
       <c r="S103" t="n">
-        <v>0.9005000000000001</v>
+        <v>0.8475</v>
       </c>
       <c r="T103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U103" t="n">
-        <v>3.24</v>
+        <v>5.03</v>
       </c>
       <c r="V103" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="W103" t="n">
-        <v>3.16</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="104">
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="P104" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="Q104" t="n">
         <v>0.86</v>
@@ -8861,19 +8861,19 @@
         <v>0.89</v>
       </c>
       <c r="S104" t="n">
-        <v>0.8485</v>
+        <v>0.9005</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="V104" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="W104" t="n">
-        <v>4.47</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="105">
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="P105" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -8942,19 +8942,19 @@
         <v>0.89</v>
       </c>
       <c r="S105" t="n">
-        <v>0.883</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>4.43</v>
+        <v>4.17</v>
       </c>
       <c r="V105" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="W105" t="n">
-        <v>4.32</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="106">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P106" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q106" t="n">
         <v>0.78</v>
@@ -9023,19 +9023,19 @@
         <v>0.92</v>
       </c>
       <c r="S106" t="n">
-        <v>0.8565</v>
+        <v>0.905</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>
       </c>
       <c r="U106" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="V106" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="W106" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
     </row>
   </sheetData>

--- a/Scenario Files/HVACRagScenarios.xlsx
+++ b/Scenario Files/HVACRagScenarios.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0.92</v>
@@ -599,7 +599,7 @@
         <v>0.84</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6575</v>
+        <v>0.6055</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="P3" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="Q3" t="n">
         <v>0.83</v>
@@ -680,7 +680,7 @@
         <v>0.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6625</v>
+        <v>0.6105</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="Q4" t="n">
         <v>0.51</v>
@@ -761,7 +761,7 @@
         <v>0.84</v>
       </c>
       <c r="S4" t="n">
-        <v>0.621</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="P5" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="Q5" t="n">
         <v>0.51</v>
@@ -842,19 +842,19 @@
         <v>0.61</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3805</v>
+        <v>0.574</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>12.96</v>
+        <v>7.68</v>
       </c>
       <c r="V5" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>13.21</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="6">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="P6" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="Q6" t="n">
         <v>0.78</v>
@@ -923,19 +923,19 @@
         <v>0.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3735</v>
+        <v>0.5825</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>14.11</v>
+        <v>8.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.68</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>14.38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="P7" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1004,19 +1004,19 @@
         <v>0.61</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3655</v>
+        <v>0.581</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>15.26</v>
+        <v>9.98</v>
       </c>
       <c r="V7" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
-        <v>15.55</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="8">
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="P8" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
         <v>0.61</v>
@@ -1085,19 +1085,19 @@
         <v>0.61</v>
       </c>
       <c r="S8" t="n">
-        <v>0.305</v>
+        <v>0.5875</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>15.32</v>
+        <v>7.8</v>
       </c>
       <c r="V8" t="n">
-        <v>2.91</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>15.61</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="9">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>0.49</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0.86</v>
@@ -1166,19 +1166,19 @@
         <v>0.61</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3</v>
+        <v>0.5855</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>16.61</v>
+        <v>9.09</v>
       </c>
       <c r="V9" t="n">
-        <v>3.16</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>16.93</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="10">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="Q10" t="n">
         <v>0.93</v>
@@ -1247,19 +1247,19 @@
         <v>0.61</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2775</v>
+        <v>0.5475</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>17.9</v>
+        <v>10.38</v>
       </c>
       <c r="V10" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="W10" t="n">
-        <v>18.25</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="11">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="Q11" t="n">
         <v>0.83</v>
@@ -1328,7 +1328,7 @@
         <v>0.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.618</v>
+        <v>0.5725</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0.92</v>
@@ -1409,7 +1409,7 @@
         <v>0.78</v>
       </c>
       <c r="S12" t="n">
-        <v>0.662</v>
+        <v>0.61</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="Q13" t="n">
         <v>0.63</v>
@@ -1490,7 +1490,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6345</v>
+        <v>0.5825</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6465</v>
+        <v>0.598</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="Q15" t="n">
         <v>0.86</v>
@@ -1652,7 +1652,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.635</v>
+        <v>0.5865</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="Q16" t="n">
         <v>0.7</v>
@@ -1733,7 +1733,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5705</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="P17" t="n">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0.51</v>
@@ -1814,19 +1814,19 @@
         <v>0.57</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5615</v>
+        <v>0.779</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>9.15</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.74</v>
+        <v>0.47</v>
       </c>
       <c r="W17" t="n">
-        <v>9.33</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="18">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.51</v>
+        <v>0.85</v>
       </c>
       <c r="P18" t="n">
-        <v>0.52</v>
+        <v>0.85</v>
       </c>
       <c r="Q18" t="n">
         <v>0.78</v>
@@ -1895,19 +1895,19 @@
         <v>0.57</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5765</v>
+        <v>0.794</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>9.99</v>
+        <v>3.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9</v>
+        <v>0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>10.18</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1976,19 +1976,19 @@
         <v>0.57</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5815</v>
+        <v>0.8055</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>10.82</v>
+        <v>4.17</v>
       </c>
       <c r="V19" t="n">
-        <v>2.06</v>
+        <v>0.79</v>
       </c>
       <c r="W19" t="n">
-        <v>11.03</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="20">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
@@ -2057,7 +2057,7 @@
         <v>0.83</v>
       </c>
       <c r="S20" t="n">
-        <v>0.708</v>
+        <v>0.653</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="P21" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="Q21" t="n">
         <v>0.93</v>
@@ -2138,7 +2138,7 @@
         <v>0.83</v>
       </c>
       <c r="S21" t="n">
-        <v>0.704</v>
+        <v>0.652</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="P22" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="Q22" t="n">
         <v>0.86</v>
@@ -2219,7 +2219,7 @@
         <v>0.83</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6995</v>
+        <v>0.6445</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="P23" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="Q23" t="n">
         <v>0.51</v>
@@ -2300,19 +2300,19 @@
         <v>0.64</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4875</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>11.05</v>
+        <v>4.82</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1</v>
+        <v>0.92</v>
       </c>
       <c r="W23" t="n">
-        <v>11.27</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="24">
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="P24" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="Q24" t="n">
         <v>0.93</v>
@@ -2381,19 +2381,19 @@
         <v>0.64</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>13.33</v>
+        <v>7.1</v>
       </c>
       <c r="V24" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>13.59</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="25">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="P25" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="Q25" t="n">
         <v>0.29</v>
@@ -2462,19 +2462,19 @@
         <v>0.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2115</v>
+        <v>0.442</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>15.61</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>2.97</v>
+        <v>1.78</v>
       </c>
       <c r="W25" t="n">
-        <v>15.91</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="26">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="P26" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="Q26" t="n">
         <v>0.93</v>
@@ -2543,19 +2543,19 @@
         <v>0.67</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8295</v>
+        <v>0.917</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>5.55</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>0.27</v>
       </c>
       <c r="W26" t="n">
-        <v>5.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.51</v>
@@ -2624,19 +2624,19 @@
         <v>0.67</v>
       </c>
       <c r="S27" t="n">
-        <v>0.781</v>
+        <v>0.8525</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>4.72</v>
+        <v>0.61</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9</v>
+        <v>0.12</v>
       </c>
       <c r="W27" t="n">
-        <v>4.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="28">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2705,19 +2705,19 @@
         <v>0.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6625</v>
+        <v>0.698</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="P29" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="Q29" t="n">
         <v>0.51</v>
@@ -2786,19 +2786,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>5.49</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="W29" t="n">
-        <v>5.36</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30">
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>0.78</v>
@@ -2867,19 +2867,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>0.783</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>5.97</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>0.38</v>
       </c>
       <c r="W30" t="n">
-        <v>5.83</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="31">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="P31" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="Q31" t="n">
         <v>0.93</v>
@@ -2948,19 +2948,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>0.797</v>
+        <v>0.8875</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>6.29</v>
+        <v>2.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>0.44</v>
       </c>
       <c r="W31" t="n">
-        <v>6.14</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="32">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="P32" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="Q32" t="n">
         <v>0.78</v>
@@ -3029,7 +3029,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8655</v>
+        <v>0.791</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
@@ -3110,7 +3110,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>0.912</v>
+        <v>0.8375</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="P34" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -3191,7 +3191,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0.879</v>
+        <v>0.801</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0.45</v>
@@ -3272,7 +3272,7 @@
         <v>0.67</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1975</v>
+        <v>0.1905</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3353,7 +3353,7 @@
         <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>0.444</v>
+        <v>0.418</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="P37" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="Q37" t="n">
         <v>0.76</v>
@@ -3434,7 +3434,7 @@
         <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>0.4575</v>
+        <v>0.422</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="P38" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="Q38" t="n">
         <v>0.78</v>
@@ -3515,7 +3515,7 @@
         <v>0.85</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7805</v>
+        <v>0.7125</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="Q39" t="n">
         <v>0.93</v>
@@ -3596,7 +3596,7 @@
         <v>0.85</v>
       </c>
       <c r="S39" t="n">
-        <v>0.8265</v>
+        <v>0.7585</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="Q40" t="n">
         <v>0.51</v>
@@ -3677,7 +3677,7 @@
         <v>0.85</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7655</v>
+        <v>0.6975</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="P41" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="Q41" t="n">
         <v>0.41</v>
@@ -3758,19 +3758,19 @@
         <v>0.63</v>
       </c>
       <c r="S41" t="n">
-        <v>0.4205</v>
+        <v>0.6445</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>12.02</v>
+        <v>5.48</v>
       </c>
       <c r="V41" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>12.26</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="42">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="P42" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="Q42" t="n">
         <v>0.78</v>
@@ -3839,19 +3839,19 @@
         <v>0.63</v>
       </c>
       <c r="S42" t="n">
-        <v>0.43</v>
+        <v>0.6635</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>13.39</v>
+        <v>6.84</v>
       </c>
       <c r="V42" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>13.65</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="43">
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="P43" t="n">
-        <v>0.15</v>
+        <v>0.51</v>
       </c>
       <c r="Q43" t="n">
         <v>0.78</v>
@@ -3920,19 +3920,19 @@
         <v>0.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0.327</v>
+        <v>0.579</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>15.44</v>
+        <v>8.9</v>
       </c>
       <c r="V43" t="n">
-        <v>2.93</v>
+        <v>1.69</v>
       </c>
       <c r="W43" t="n">
-        <v>15.74</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="44">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="P44" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q44" t="n">
         <v>0.78</v>
@@ -4001,7 +4001,7 @@
         <v>0.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0.719</v>
+        <v>0.6605</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="P45" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="Q45" t="n">
         <v>0.93</v>
@@ -4082,7 +4082,7 @@
         <v>0.85</v>
       </c>
       <c r="S45" t="n">
-        <v>0.788</v>
+        <v>0.723</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="P46" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7</v>
@@ -4163,7 +4163,7 @@
         <v>0.85</v>
       </c>
       <c r="S46" t="n">
-        <v>0.768</v>
+        <v>0.7</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>0.51</v>
@@ -4244,19 +4244,19 @@
         <v>0.72</v>
       </c>
       <c r="S47" t="n">
-        <v>0.8175</v>
+        <v>0.86</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>0.78</v>
@@ -4325,19 +4325,19 @@
         <v>0.72</v>
       </c>
       <c r="S48" t="n">
-        <v>0.826</v>
+        <v>0.914</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
@@ -4406,19 +4406,19 @@
         <v>0.72</v>
       </c>
       <c r="S49" t="n">
-        <v>0.8245</v>
+        <v>0.958</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>5.94</v>
+        <v>0.61</v>
       </c>
       <c r="V49" t="n">
-        <v>1.13</v>
+        <v>0.12</v>
       </c>
       <c r="W49" t="n">
-        <v>6.18</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="50">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="P50" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="Q50" t="n">
         <v>0.29</v>
@@ -4487,19 +4487,19 @@
         <v>0.6</v>
       </c>
       <c r="S50" t="n">
-        <v>0.457</v>
+        <v>0.642</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>10.58</v>
+        <v>4.82</v>
       </c>
       <c r="V50" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="W50" t="n">
-        <v>10.79</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="51">
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="P51" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="Q51" t="n">
         <v>0.78</v>
@@ -4568,19 +4568,19 @@
         <v>0.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0.4965</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>11.88</v>
+        <v>6.12</v>
       </c>
       <c r="V51" t="n">
-        <v>2.26</v>
+        <v>1.16</v>
       </c>
       <c r="W51" t="n">
-        <v>12.11</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="52">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P52" t="n">
-        <v>0.26</v>
+        <v>0.57</v>
       </c>
       <c r="Q52" t="n">
         <v>0.7</v>
@@ -4649,19 +4649,19 @@
         <v>0.6</v>
       </c>
       <c r="S52" t="n">
-        <v>0.387</v>
+        <v>0.5975</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>13.71</v>
+        <v>7.94</v>
       </c>
       <c r="V52" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="W52" t="n">
-        <v>13.97</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="53">
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4730,19 +4730,19 @@
         <v>0.72</v>
       </c>
       <c r="S53" t="n">
-        <v>0.4825</v>
+        <v>0.638</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>9.33</v>
+        <v>4.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.77</v>
+        <v>0.76</v>
       </c>
       <c r="W53" t="n">
-        <v>9.109999999999999</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="54">
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="P54" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="Q54" t="n">
         <v>0.46</v>
@@ -4811,19 +4811,19 @@
         <v>0.72</v>
       </c>
       <c r="S54" t="n">
-        <v>0.5455</v>
+        <v>0.704</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>9.98</v>
+        <v>4.66</v>
       </c>
       <c r="V54" t="n">
-        <v>1.9</v>
+        <v>0.88</v>
       </c>
       <c r="W54" t="n">
-        <v>9.74</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="55">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="P55" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="Q55" t="n">
         <v>0.8100000000000001</v>
@@ -4892,19 +4892,19 @@
         <v>0.72</v>
       </c>
       <c r="S55" t="n">
-        <v>0.5895</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>10.62</v>
+        <v>5.3</v>
       </c>
       <c r="V55" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="W55" t="n">
-        <v>10.37</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="56">
@@ -5141,13 +5141,13 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5222,13 +5222,13 @@
         <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5300,16 +5300,16 @@
         <v>0.929</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>0.93</v>
@@ -5378,19 +5378,19 @@
         <v>0.82</v>
       </c>
       <c r="S61" t="n">
-        <v>0.92</v>
+        <v>0.959</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5870,13 +5870,13 @@
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="P68" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="Q68" t="n">
         <v>0.18</v>
@@ -5945,7 +5945,7 @@
         <v>0.64</v>
       </c>
       <c r="S68" t="n">
-        <v>0.639</v>
+        <v>0.574</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="P69" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="Q69" t="n">
         <v>0.67</v>
@@ -6026,7 +6026,7 @@
         <v>0.85</v>
       </c>
       <c r="S69" t="n">
-        <v>0.8105</v>
+        <v>0.736</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="P70" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
@@ -6107,7 +6107,7 @@
         <v>0.85</v>
       </c>
       <c r="S70" t="n">
-        <v>0.9155</v>
+        <v>0.841</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="P71" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -6188,7 +6188,7 @@
         <v>0.89</v>
       </c>
       <c r="S71" t="n">
-        <v>0.8955</v>
+        <v>0.824</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="Q72" t="n">
         <v>0.7</v>
@@ -6269,7 +6269,7 @@
         <v>0.89</v>
       </c>
       <c r="S72" t="n">
-        <v>0.8615</v>
+        <v>0.7835</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P73" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q73" t="n">
         <v>0.41</v>
@@ -6350,7 +6350,7 @@
         <v>0.78</v>
       </c>
       <c r="S73" t="n">
-        <v>0.8</v>
+        <v>0.7255</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P74" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="Q74" t="n">
         <v>0.86</v>
@@ -6431,7 +6431,7 @@
         <v>0.86</v>
       </c>
       <c r="S74" t="n">
-        <v>0.912</v>
+        <v>0.834</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="P75" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="Q75" t="n">
         <v>0.93</v>
@@ -6512,7 +6512,7 @@
         <v>0.86</v>
       </c>
       <c r="S75" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.861</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="P76" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="Q76" t="n">
         <v>0.61</v>
@@ -6593,7 +6593,7 @@
         <v>0.86</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8975</v>
+        <v>0.8165</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="P77" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q77" t="n">
         <v>0.92</v>
@@ -6674,7 +6674,7 @@
         <v>0.9</v>
       </c>
       <c r="S77" t="n">
-        <v>0.7575</v>
+        <v>0.696</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="P78" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="Q78" t="n">
         <v>0.51</v>
@@ -6755,7 +6755,7 @@
         <v>0.9</v>
       </c>
       <c r="S78" t="n">
-        <v>0.7145</v>
+        <v>0.6465</v>
       </c>
       <c r="T78" t="n">
         <v>2</v>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="P79" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="Q79" t="n">
         <v>0.06</v>
@@ -6836,7 +6836,7 @@
         <v>0.67</v>
       </c>
       <c r="S79" t="n">
-        <v>0.616</v>
+        <v>0.548</v>
       </c>
       <c r="T79" t="n">
         <v>3</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="P80" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="Q80" t="n">
         <v>0.86</v>
@@ -6917,7 +6917,7 @@
         <v>0.77</v>
       </c>
       <c r="S80" t="n">
-        <v>0.843</v>
+        <v>0.7685</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="P81" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="Q81" t="n">
         <v>0.61</v>
@@ -6998,7 +6998,7 @@
         <v>0.84</v>
       </c>
       <c r="S81" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="P82" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="Q82" t="n">
         <v>0.29</v>
@@ -7079,7 +7079,7 @@
         <v>0.63</v>
       </c>
       <c r="S82" t="n">
-        <v>0.7275</v>
+        <v>0.653</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="P83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7160,19 +7160,19 @@
         <v>0.29</v>
       </c>
       <c r="S83" t="n">
-        <v>0.495</v>
+        <v>0.599</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>7.27</v>
+        <v>3.29</v>
       </c>
       <c r="V83" t="n">
-        <v>1.38</v>
+        <v>0.63</v>
       </c>
       <c r="W83" t="n">
-        <v>7.57</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="84">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P84" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q84" t="n">
         <v>0.29</v>
@@ -7241,19 +7241,19 @@
         <v>0.62</v>
       </c>
       <c r="S84" t="n">
-        <v>0.5765</v>
+        <v>0.6775</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>7.95</v>
+        <v>3.98</v>
       </c>
       <c r="V84" t="n">
-        <v>1.51</v>
+        <v>0.76</v>
       </c>
       <c r="W84" t="n">
-        <v>8.279999999999999</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="85">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="P85" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="Q85" t="n">
         <v>0.61</v>
@@ -7322,19 +7322,19 @@
         <v>0.62</v>
       </c>
       <c r="S85" t="n">
-        <v>0.608</v>
+        <v>0.7155</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>8.630000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="V85" t="n">
-        <v>1.64</v>
+        <v>0.89</v>
       </c>
       <c r="W85" t="n">
-        <v>8.99</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="86">
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="P86" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q86" t="n">
         <v>0.78</v>
@@ -7403,7 +7403,7 @@
         <v>0.84</v>
       </c>
       <c r="S86" t="n">
-        <v>0.7175</v>
+        <v>0.659</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="P87" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -7484,7 +7484,7 @@
         <v>0.84</v>
       </c>
       <c r="S87" t="n">
-        <v>0.781</v>
+        <v>0.7195</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="P88" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="Q88" t="n">
         <v>0.78</v>
@@ -7565,7 +7565,7 @@
         <v>0.88</v>
       </c>
       <c r="S88" t="n">
-        <v>0.7625</v>
+        <v>0.701</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="P89" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0.29</v>
       </c>
       <c r="S89" t="n">
-        <v>0.5435</v>
+        <v>0.6415</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>6.27</v>
+        <v>2.27</v>
       </c>
       <c r="V89" t="n">
-        <v>1.19</v>
+        <v>0.43</v>
       </c>
       <c r="W89" t="n">
-        <v>6.53</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="90">
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="P90" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="Q90" t="n">
         <v>0.29</v>
@@ -7727,19 +7727,19 @@
         <v>0.61</v>
       </c>
       <c r="S90" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>6.96</v>
+        <v>2.96</v>
       </c>
       <c r="V90" t="n">
-        <v>1.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W90" t="n">
-        <v>7.24</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="91">
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="P91" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="Q91" t="n">
         <v>0.61</v>
@@ -7808,19 +7808,19 @@
         <v>0.61</v>
       </c>
       <c r="S91" t="n">
-        <v>0.652</v>
+        <v>0.753</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>7.65</v>
+        <v>3.65</v>
       </c>
       <c r="V91" t="n">
-        <v>1.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W91" t="n">
-        <v>7.96</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="92">
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="P92" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
@@ -7889,7 +7889,7 @@
         <v>0.8</v>
       </c>
       <c r="S92" t="n">
-        <v>0.5705</v>
+        <v>0.5315</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="P93" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="Q93" t="n">
         <v>0.76</v>
@@ -7970,7 +7970,7 @@
         <v>0.8</v>
       </c>
       <c r="S93" t="n">
-        <v>0.5615</v>
+        <v>0.516</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="P94" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Q94" t="n">
         <v>0.45</v>
@@ -8051,7 +8051,7 @@
         <v>0.8</v>
       </c>
       <c r="S94" t="n">
-        <v>0.535</v>
+        <v>0.4865</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P95" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8132,19 +8132,19 @@
         <v>0.25</v>
       </c>
       <c r="S95" t="n">
-        <v>0.369</v>
+        <v>0.4825</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>9.9</v>
+        <v>5.96</v>
       </c>
       <c r="V95" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="W95" t="n">
-        <v>10.31</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="96">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="P96" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="Q96" t="n">
         <v>0.41</v>
@@ -8213,19 +8213,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>0.422</v>
+        <v>0.569</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>10.96</v>
+        <v>7.02</v>
       </c>
       <c r="V96" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="W96" t="n">
-        <v>11.41</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="97">
@@ -8282,10 +8282,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P97" t="n">
-        <v>0.36</v>
+        <v>0.55</v>
       </c>
       <c r="Q97" t="n">
         <v>0.78</v>
@@ -8294,19 +8294,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>0.426</v>
+        <v>0.6005</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>12.01</v>
+        <v>8.07</v>
       </c>
       <c r="V97" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="W97" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="98">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="P98" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="Q98" t="n">
         <v>0.7</v>
@@ -8375,7 +8375,7 @@
         <v>0.78</v>
       </c>
       <c r="S98" t="n">
-        <v>0.677</v>
+        <v>0.6185</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="P99" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q99" t="n">
         <v>0.93</v>
@@ -8456,7 +8456,7 @@
         <v>0.78</v>
       </c>
       <c r="S99" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="P100" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="Q100" t="n">
         <v>0.86</v>
@@ -8537,7 +8537,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S100" t="n">
-        <v>0.762</v>
+        <v>0.7005</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
         <v>0.41</v>
@@ -8618,19 +8618,19 @@
         <v>0.78</v>
       </c>
       <c r="S101" t="n">
-        <v>0.8165</v>
+        <v>0.849</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>3.84</v>
+        <v>0.24</v>
       </c>
       <c r="V101" t="n">
-        <v>0.73</v>
+        <v>0.05</v>
       </c>
       <c r="W101" t="n">
-        <v>3.75</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="102">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="n">
         <v>0.7</v>
@@ -8699,19 +8699,19 @@
         <v>0.78</v>
       </c>
       <c r="S102" t="n">
-        <v>0.8485</v>
+        <v>0.907</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>4.44</v>
+        <v>0.84</v>
       </c>
       <c r="V102" t="n">
-        <v>0.84</v>
+        <v>0.16</v>
       </c>
       <c r="W102" t="n">
-        <v>4.33</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="103">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="P103" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="Q103" t="n">
         <v>0.93</v>
@@ -8780,19 +8780,19 @@
         <v>0.66</v>
       </c>
       <c r="S103" t="n">
-        <v>0.8475</v>
+        <v>0.9155</v>
       </c>
       <c r="T103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>5.03</v>
+        <v>1.43</v>
       </c>
       <c r="V103" t="n">
-        <v>0.96</v>
+        <v>0.27</v>
       </c>
       <c r="W103" t="n">
-        <v>4.91</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="104">
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="P104" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="Q104" t="n">
         <v>0.86</v>
@@ -8861,7 +8861,7 @@
         <v>0.89</v>
       </c>
       <c r="S104" t="n">
-        <v>0.9005</v>
+        <v>0.8225</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="P105" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -8942,7 +8942,7 @@
         <v>0.89</v>
       </c>
       <c r="S105" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P106" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="Q106" t="n">
         <v>0.78</v>
@@ -9023,7 +9023,7 @@
         <v>0.92</v>
       </c>
       <c r="S106" t="n">
-        <v>0.905</v>
+        <v>0.8275</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>

--- a/Scenario Files/HVACRagScenarios.xlsx
+++ b/Scenario Files/HVACRagScenarios.xlsx
@@ -587,31 +587,31 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="P2" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="Q2" t="n">
         <v>0.92</v>
       </c>
       <c r="R2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6055</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>9.65</v>
+        <v>7.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>10.05</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="3">
@@ -668,31 +668,31 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="P3" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="Q3" t="n">
         <v>0.83</v>
       </c>
       <c r="R3" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6105</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>9.109999999999999</v>
+        <v>6.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>9.48</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="4">
@@ -749,31 +749,31 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="P4" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="Q4" t="n">
         <v>0.51</v>
       </c>
       <c r="R4" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.6575</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>8.56</v>
+        <v>6.23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>8.91</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="P5" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="Q5" t="n">
         <v>0.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S5" t="n">
-        <v>0.574</v>
+        <v>0.359</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>7.68</v>
+        <v>11.48</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>2.18</v>
       </c>
       <c r="W5" t="n">
-        <v>7.83</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="6">
@@ -911,31 +911,31 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="Q6" t="n">
         <v>0.78</v>
       </c>
       <c r="R6" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5825</v>
+        <v>0.3485</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>8.83</v>
+        <v>12.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="W6" t="n">
-        <v>9</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="7">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S7" t="n">
-        <v>0.581</v>
+        <v>0.334</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>9.98</v>
+        <v>13.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="W7" t="n">
-        <v>10.17</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="8">
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.57</v>
+        <v>0.18</v>
       </c>
       <c r="P8" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5875</v>
+        <v>0.327</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>7.8</v>
+        <v>12.45</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>2.36</v>
       </c>
       <c r="W8" t="n">
-        <v>7.95</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.49</v>
+        <v>0.08</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5855</v>
+        <v>0.312</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>9.09</v>
+        <v>13.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="W9" t="n">
-        <v>9.27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.42</v>
+        <v>0.01</v>
       </c>
       <c r="Q10" t="n">
         <v>0.93</v>
       </c>
       <c r="R10" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5475</v>
+        <v>0.2705</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>10.38</v>
+        <v>15.03</v>
       </c>
       <c r="V10" t="n">
-        <v>1.97</v>
+        <v>2.86</v>
       </c>
       <c r="W10" t="n">
-        <v>10.58</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="11">
@@ -1316,31 +1316,31 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="P11" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="Q11" t="n">
         <v>0.83</v>
       </c>
       <c r="R11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5725</v>
+        <v>0.622</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>9.949999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>10.15</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="P12" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="Q12" t="n">
         <v>0.92</v>
       </c>
       <c r="R12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S12" t="n">
-        <v>0.61</v>
+        <v>0.6695</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>9.4</v>
+        <v>7.42</v>
       </c>
       <c r="V12" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>9.58</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="13">
@@ -1478,31 +1478,31 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="Q13" t="n">
         <v>0.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5825</v>
+        <v>0.645</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>8.84</v>
+        <v>6.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>9.01</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
@@ -1559,31 +1559,31 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="P14" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0.598</v>
+        <v>0.705</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>10.21</v>
+        <v>7.03</v>
       </c>
       <c r="V14" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="15">
@@ -1640,31 +1640,31 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="P15" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="Q15" t="n">
         <v>0.86</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5865</v>
+        <v>0.6965</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>9.83</v>
+        <v>6.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>10.02</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="16">
@@ -1721,31 +1721,31 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="P16" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="Q16" t="n">
         <v>0.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5705</v>
+        <v>0.6805</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>9.449999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="V16" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="W16" t="n">
-        <v>9.630000000000001</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="17">
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.91</v>
+        <v>0.55</v>
       </c>
       <c r="P17" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q17" t="n">
         <v>0.51</v>
       </c>
       <c r="R17" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="S17" t="n">
-        <v>0.779</v>
+        <v>0.544</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>7.77</v>
       </c>
       <c r="V17" t="n">
-        <v>0.47</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>2.55</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="18">
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="P18" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="S18" t="n">
-        <v>0.794</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3.33</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.63</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>3.4</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="19">
@@ -1964,31 +1964,31 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8</v>
+        <v>0.43</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8055</v>
+        <v>0.5575</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>4.17</v>
+        <v>9.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0.79</v>
+        <v>1.79</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2045,31 +2045,31 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="P20" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="S20" t="n">
-        <v>0.653</v>
+        <v>0.7105</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>8.890000000000001</v>
+        <v>7.09</v>
       </c>
       <c r="V20" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>9.06</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="21">
@@ -2126,31 +2126,31 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="P21" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="Q21" t="n">
         <v>0.93</v>
       </c>
       <c r="R21" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0.652</v>
+        <v>0.7065</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>8.69</v>
+        <v>6.89</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>8.859999999999999</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="22">
@@ -2207,31 +2207,31 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="P22" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="Q22" t="n">
         <v>0.86</v>
       </c>
       <c r="R22" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6445</v>
+        <v>0.702</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>8.49</v>
+        <v>6.69</v>
       </c>
       <c r="V22" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>8.66</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="23">
@@ -2288,31 +2288,31 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="Q23" t="n">
         <v>0.51</v>
       </c>
       <c r="R23" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>4.82</v>
+        <v>8.68</v>
       </c>
       <c r="V23" t="n">
-        <v>0.92</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>4.91</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="24">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
       <c r="P24" t="n">
-        <v>0.62</v>
+        <v>0.32</v>
       </c>
       <c r="Q24" t="n">
         <v>0.93</v>
       </c>
       <c r="R24" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.475</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>7.1</v>
+        <v>10.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="W24" t="n">
-        <v>7.23</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="25">
@@ -2450,31 +2450,31 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="P25" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="Q25" t="n">
         <v>0.29</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="S25" t="n">
-        <v>0.442</v>
+        <v>0.2105</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>9.380000000000001</v>
+        <v>13.24</v>
       </c>
       <c r="V25" t="n">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="W25" t="n">
-        <v>9.56</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="26">
@@ -2531,31 +2531,31 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="P26" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Q26" t="n">
         <v>0.93</v>
       </c>
       <c r="R26" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S26" t="n">
-        <v>0.917</v>
+        <v>0.8395</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>3.99</v>
       </c>
       <c r="V26" t="n">
-        <v>0.27</v>
+        <v>0.76</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="27">
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="Q27" t="n">
         <v>0.51</v>
       </c>
       <c r="R27" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8525</v>
+        <v>0.7975</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0.61</v>
+        <v>3.16</v>
       </c>
       <c r="V27" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0.59</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="28">
@@ -2693,31 +2693,31 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="S28" t="n">
-        <v>0.698</v>
+        <v>0.6835</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="29">
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Q29" t="n">
         <v>0.51</v>
       </c>
       <c r="R29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S29" t="n">
-        <v>0.836</v>
+        <v>0.76</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>3.99</v>
       </c>
       <c r="V29" t="n">
-        <v>0.29</v>
+        <v>0.76</v>
       </c>
       <c r="W29" t="n">
-        <v>1.5</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="30">
@@ -2855,31 +2855,31 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="Q30" t="n">
         <v>0.78</v>
       </c>
       <c r="R30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.7915</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>4.47</v>
       </c>
       <c r="V30" t="n">
-        <v>0.38</v>
+        <v>0.85</v>
       </c>
       <c r="W30" t="n">
-        <v>1.97</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="31">
@@ -2936,31 +2936,31 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
         <v>0.93</v>
       </c>
       <c r="R31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8875</v>
+        <v>0.805</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.34</v>
+        <v>4.79</v>
       </c>
       <c r="V31" t="n">
-        <v>0.44</v>
+        <v>0.91</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="32">
@@ -3017,31 +3017,31 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="P32" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="Q32" t="n">
         <v>0.78</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="S32" t="n">
-        <v>0.791</v>
+        <v>0.9</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>4.81</v>
+        <v>2.97</v>
       </c>
       <c r="V32" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>4.91</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="33">
@@ -3098,31 +3098,31 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="P33" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8375</v>
+        <v>0.946</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4.45</v>
+        <v>2.61</v>
       </c>
       <c r="V33" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="W33" t="n">
-        <v>4.54</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="34">
@@ -3179,31 +3179,31 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="S34" t="n">
-        <v>0.801</v>
+        <v>0.913</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>4.19</v>
+        <v>2.34</v>
       </c>
       <c r="V34" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="W34" t="n">
-        <v>4.27</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="35">
@@ -3263,28 +3263,28 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q35" t="n">
         <v>0.45</v>
       </c>
       <c r="R35" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1905</v>
+        <v>0.184</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>17.25</v>
+        <v>14.79</v>
       </c>
       <c r="V35" t="n">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="W35" t="n">
-        <v>17.58</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="36">
@@ -3341,31 +3341,31 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="P36" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S36" t="n">
-        <v>0.418</v>
+        <v>0.445</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>14.64</v>
+        <v>12.18</v>
       </c>
       <c r="V36" t="n">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="W36" t="n">
-        <v>14.92</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="37">
@@ -3422,31 +3422,31 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="P37" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="Q37" t="n">
         <v>0.76</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S37" t="n">
-        <v>0.422</v>
+        <v>0.462</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>13.33</v>
+        <v>10.87</v>
       </c>
       <c r="V37" t="n">
-        <v>2.53</v>
+        <v>2.07</v>
       </c>
       <c r="W37" t="n">
-        <v>13.59</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="38">
@@ -3503,31 +3503,31 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="P38" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="Q38" t="n">
         <v>0.78</v>
       </c>
       <c r="R38" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7125</v>
+        <v>0.7905</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>6.41</v>
+        <v>4.74</v>
       </c>
       <c r="V38" t="n">
-        <v>1.22</v>
+        <v>0.9</v>
       </c>
       <c r="W38" t="n">
-        <v>6.67</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="39">
@@ -3584,31 +3584,31 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="P39" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="Q39" t="n">
         <v>0.93</v>
       </c>
       <c r="R39" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7585</v>
+        <v>0.8465</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>5.98</v>
+        <v>4.31</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="W39" t="n">
-        <v>6.23</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="40">
@@ -3665,31 +3665,31 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="P40" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="Q40" t="n">
         <v>0.51</v>
       </c>
       <c r="R40" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="S40" t="n">
-        <v>0.6975</v>
+        <v>0.7885</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>5.45</v>
+        <v>3.79</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>0.72</v>
       </c>
       <c r="W40" t="n">
-        <v>5.68</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="41">
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
       <c r="P41" t="n">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
       <c r="Q41" t="n">
         <v>0.41</v>
       </c>
       <c r="R41" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="S41" t="n">
-        <v>0.6445</v>
+        <v>0.4365</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>5.48</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="W41" t="n">
-        <v>5.58</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3827,31 +3827,31 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="P42" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="Q42" t="n">
         <v>0.78</v>
       </c>
       <c r="R42" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6635</v>
+        <v>0.442</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>6.84</v>
+        <v>10.9</v>
       </c>
       <c r="V42" t="n">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="W42" t="n">
-        <v>6.98</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="43">
@@ -3908,31 +3908,31 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="P43" t="n">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="Q43" t="n">
         <v>0.78</v>
       </c>
       <c r="R43" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="S43" t="n">
-        <v>0.579</v>
+        <v>0.338</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>8.9</v>
+        <v>12.95</v>
       </c>
       <c r="V43" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="W43" t="n">
-        <v>9.07</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="44">
@@ -3989,31 +3989,31 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="P44" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="Q44" t="n">
         <v>0.78</v>
       </c>
       <c r="R44" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="S44" t="n">
-        <v>0.6605</v>
+        <v>0.735</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>7.74</v>
+        <v>5.72</v>
       </c>
       <c r="V44" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="W44" t="n">
-        <v>7.89</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="45">
@@ -4070,31 +4070,31 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="P45" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="Q45" t="n">
         <v>0.93</v>
       </c>
       <c r="R45" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="S45" t="n">
-        <v>0.723</v>
+        <v>0.804</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.93</v>
+        <v>4.91</v>
       </c>
       <c r="V45" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="W45" t="n">
-        <v>7.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -4151,31 +4151,31 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.66</v>
+        <v>0.83</v>
       </c>
       <c r="P46" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="S46" t="n">
-        <v>0.7</v>
+        <v>0.7905</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>6.33</v>
+        <v>4.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>0.82</v>
       </c>
       <c r="W46" t="n">
-        <v>6.45</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="47">
@@ -4232,31 +4232,31 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="Q47" t="n">
         <v>0.51</v>
       </c>
       <c r="R47" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="S47" t="n">
-        <v>0.86</v>
+        <v>0.8055</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="48">
@@ -4313,31 +4313,31 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="Q48" t="n">
         <v>0.78</v>
       </c>
       <c r="R48" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="S48" t="n">
-        <v>0.914</v>
+        <v>0.8075</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="49">
@@ -4394,31 +4394,31 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="S49" t="n">
-        <v>0.958</v>
+        <v>0.806</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>0.61</v>
+        <v>4.83</v>
       </c>
       <c r="V49" t="n">
-        <v>0.12</v>
+        <v>0.92</v>
       </c>
       <c r="W49" t="n">
-        <v>0.63</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="50">
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="Q50" t="n">
         <v>0.29</v>
       </c>
       <c r="R50" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="S50" t="n">
-        <v>0.642</v>
+        <v>0.4675</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>4.82</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="V50" t="n">
-        <v>0.92</v>
+        <v>1.59</v>
       </c>
       <c r="W50" t="n">
-        <v>4.91</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4556,31 +4556,31 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="P51" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="Q51" t="n">
         <v>0.78</v>
       </c>
       <c r="R51" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="S51" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>6.12</v>
+        <v>9.69</v>
       </c>
       <c r="V51" t="n">
-        <v>1.16</v>
+        <v>1.84</v>
       </c>
       <c r="W51" t="n">
-        <v>6.24</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="P52" t="n">
-        <v>0.57</v>
+        <v>0.27</v>
       </c>
       <c r="Q52" t="n">
         <v>0.7</v>
       </c>
       <c r="R52" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="S52" t="n">
-        <v>0.5975</v>
+        <v>0.3935</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>7.94</v>
+        <v>11.52</v>
       </c>
       <c r="V52" t="n">
-        <v>1.51</v>
+        <v>2.19</v>
       </c>
       <c r="W52" t="n">
-        <v>8.09</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="53">
@@ -4718,31 +4718,31 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="P53" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="S53" t="n">
-        <v>0.638</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>4.01</v>
+        <v>7.29</v>
       </c>
       <c r="V53" t="n">
-        <v>0.76</v>
+        <v>1.39</v>
       </c>
       <c r="W53" t="n">
-        <v>3.91</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="54">
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.77</v>
+        <v>0.54</v>
       </c>
       <c r="P54" t="n">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
       <c r="Q54" t="n">
         <v>0.46</v>
       </c>
       <c r="R54" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="S54" t="n">
-        <v>0.704</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>4.66</v>
+        <v>7.94</v>
       </c>
       <c r="V54" t="n">
-        <v>0.88</v>
+        <v>1.51</v>
       </c>
       <c r="W54" t="n">
-        <v>4.54</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="55">
@@ -4880,31 +4880,31 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="P55" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q55" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="R55" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="S55" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.601</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>5.3</v>
+        <v>8.59</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="W55" t="n">
-        <v>5.17</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4970,10 +4970,10 @@
         <v>0.15</v>
       </c>
       <c r="R56" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="S56" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="T56" t="n">
         <v>3</v>
@@ -5051,10 +5051,10 @@
         <v>0.61</v>
       </c>
       <c r="R57" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S57" t="n">
-        <v>0.9085</v>
+        <v>0.9055</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -5132,10 +5132,10 @@
         <v>0.86</v>
       </c>
       <c r="R58" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S58" t="n">
-        <v>0.9585</v>
+        <v>0.9555</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
@@ -5213,10 +5213,10 @@
         <v>0.51</v>
       </c>
       <c r="R59" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="S59" t="n">
-        <v>0.875</v>
+        <v>0.8585</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
@@ -5294,22 +5294,22 @@
         <v>0.78</v>
       </c>
       <c r="R60" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="S60" t="n">
-        <v>0.929</v>
+        <v>0.9125</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="61">
@@ -5375,22 +5375,22 @@
         <v>0.93</v>
       </c>
       <c r="R61" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="S61" t="n">
-        <v>0.959</v>
+        <v>0.9425</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="62">
@@ -5456,10 +5456,10 @@
         <v>0.78</v>
       </c>
       <c r="R62" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9425</v>
+        <v>0.9395</v>
       </c>
       <c r="T62" t="n">
         <v>2</v>
@@ -5537,10 +5537,10 @@
         <v>0.93</v>
       </c>
       <c r="R63" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9665</v>
+        <v>0.9635</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -5618,10 +5618,10 @@
         <v>0.61</v>
       </c>
       <c r="R64" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="S64" t="n">
-        <v>0.9025</v>
+        <v>0.8995</v>
       </c>
       <c r="T64" t="n">
         <v>3</v>
@@ -5699,10 +5699,10 @@
         <v>0.41</v>
       </c>
       <c r="R65" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="S65" t="n">
-        <v>0.8625</v>
+        <v>0.855</v>
       </c>
       <c r="T65" t="n">
         <v>3</v>
@@ -5780,10 +5780,10 @@
         <v>0.78</v>
       </c>
       <c r="R66" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="S66" t="n">
-        <v>0.9365</v>
+        <v>0.929</v>
       </c>
       <c r="T66" t="n">
         <v>2</v>
@@ -5861,10 +5861,10 @@
         <v>0.93</v>
       </c>
       <c r="R67" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="S67" t="n">
-        <v>0.962</v>
+        <v>0.9545</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
@@ -5933,31 +5933,31 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="Q68" t="n">
         <v>0.18</v>
       </c>
       <c r="R68" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S68" t="n">
-        <v>0.574</v>
+        <v>0.653</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>6.14</v>
+        <v>4.35</v>
       </c>
       <c r="V68" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="W68" t="n">
-        <v>6.26</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="69">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="P69" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="Q69" t="n">
         <v>0.67</v>
       </c>
       <c r="R69" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="S69" t="n">
-        <v>0.736</v>
+        <v>0.8265</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>5.27</v>
+        <v>3.48</v>
       </c>
       <c r="V69" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="W69" t="n">
-        <v>5.37</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="70">
@@ -6095,31 +6095,31 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="P70" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="S70" t="n">
-        <v>0.841</v>
+        <v>0.9345</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>4.4</v>
+        <v>2.61</v>
       </c>
       <c r="V70" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="W70" t="n">
-        <v>4.49</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="71">
@@ -6176,31 +6176,31 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="P71" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="S71" t="n">
-        <v>0.824</v>
+        <v>0.9105</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>4.88</v>
+        <v>3.38</v>
       </c>
       <c r="V71" t="n">
-        <v>0.93</v>
+        <v>0.64</v>
       </c>
       <c r="W71" t="n">
-        <v>5.08</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="72">
@@ -6257,31 +6257,31 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P72" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="Q72" t="n">
         <v>0.7</v>
       </c>
       <c r="R72" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="S72" t="n">
-        <v>0.7835</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>4.39</v>
+        <v>2.89</v>
       </c>
       <c r="V72" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="W72" t="n">
-        <v>4.57</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="73">
@@ -6338,31 +6338,31 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="P73" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="Q73" t="n">
         <v>0.41</v>
       </c>
       <c r="R73" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="S73" t="n">
-        <v>0.7255</v>
+        <v>0.823</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>4.03</v>
+        <v>2.53</v>
       </c>
       <c r="V73" t="n">
-        <v>0.77</v>
+        <v>0.48</v>
       </c>
       <c r="W73" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="74">
@@ -6419,31 +6419,31 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="P74" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="Q74" t="n">
         <v>0.86</v>
       </c>
       <c r="R74" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="S74" t="n">
-        <v>0.834</v>
+        <v>0.913</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="V74" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="W74" t="n">
-        <v>3.97</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="75">
@@ -6500,31 +6500,31 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="P75" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="Q75" t="n">
         <v>0.93</v>
       </c>
       <c r="R75" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="S75" t="n">
-        <v>0.861</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>3.57</v>
+        <v>2.23</v>
       </c>
       <c r="V75" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="W75" t="n">
-        <v>3.64</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="76">
@@ -6581,31 +6581,31 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
         <v>0.61</v>
       </c>
       <c r="R76" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8165</v>
+        <v>0.889</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>3.14</v>
+        <v>1.8</v>
       </c>
       <c r="V76" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="W76" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="77">
@@ -6662,31 +6662,31 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="P77" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="Q77" t="n">
         <v>0.92</v>
       </c>
       <c r="R77" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="S77" t="n">
-        <v>0.696</v>
+        <v>0.7725</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>7.62</v>
+        <v>5.76</v>
       </c>
       <c r="V77" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="W77" t="n">
-        <v>7.94</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="78">
@@ -6743,31 +6743,31 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="P78" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="Q78" t="n">
         <v>0.51</v>
       </c>
       <c r="R78" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="S78" t="n">
-        <v>0.6465</v>
+        <v>0.736</v>
       </c>
       <c r="T78" t="n">
         <v>2</v>
       </c>
       <c r="U78" t="n">
-        <v>6.82</v>
+        <v>4.96</v>
       </c>
       <c r="V78" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W78" t="n">
-        <v>7.1</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="79">
@@ -6824,31 +6824,31 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="P79" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q79" t="n">
         <v>0.06</v>
       </c>
       <c r="R79" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S79" t="n">
-        <v>0.548</v>
+        <v>0.639</v>
       </c>
       <c r="T79" t="n">
         <v>3</v>
       </c>
       <c r="U79" t="n">
-        <v>6.22</v>
+        <v>4.36</v>
       </c>
       <c r="V79" t="n">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="W79" t="n">
-        <v>6.48</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="80">
@@ -6905,31 +6905,31 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="P80" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="Q80" t="n">
         <v>0.86</v>
       </c>
       <c r="R80" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="S80" t="n">
-        <v>0.7685</v>
+        <v>0.8435</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>5.12</v>
+        <v>3.71</v>
       </c>
       <c r="V80" t="n">
-        <v>0.97</v>
+        <v>0.7</v>
       </c>
       <c r="W80" t="n">
-        <v>5.33</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="81">
@@ -6986,31 +6986,31 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="P81" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="Q81" t="n">
         <v>0.61</v>
       </c>
       <c r="R81" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S81" t="n">
-        <v>0.7385</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>4.86</v>
+        <v>3.45</v>
       </c>
       <c r="V81" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="W81" t="n">
-        <v>5.06</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="82">
@@ -7067,31 +7067,31 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="P82" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="Q82" t="n">
         <v>0.29</v>
       </c>
       <c r="R82" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="S82" t="n">
-        <v>0.653</v>
+        <v>0.738</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
       </c>
       <c r="U82" t="n">
-        <v>4.6</v>
+        <v>3.19</v>
       </c>
       <c r="V82" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="W82" t="n">
-        <v>4.79</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="83">
@@ -7148,31 +7148,31 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="P83" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="S83" t="n">
-        <v>0.599</v>
+        <v>0.494</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>3.29</v>
+        <v>5.76</v>
       </c>
       <c r="V83" t="n">
-        <v>0.63</v>
+        <v>1.09</v>
       </c>
       <c r="W83" t="n">
-        <v>3.43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -7229,31 +7229,31 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="P84" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="Q84" t="n">
         <v>0.29</v>
       </c>
       <c r="R84" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="S84" t="n">
-        <v>0.6775</v>
+        <v>0.5645</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>3.98</v>
+        <v>6.45</v>
       </c>
       <c r="V84" t="n">
-        <v>0.76</v>
+        <v>1.22</v>
       </c>
       <c r="W84" t="n">
-        <v>4.14</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="85">
@@ -7310,31 +7310,31 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="P85" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="Q85" t="n">
         <v>0.61</v>
       </c>
       <c r="R85" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="S85" t="n">
-        <v>0.7155</v>
+        <v>0.593</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>4.66</v>
+        <v>7.13</v>
       </c>
       <c r="V85" t="n">
-        <v>0.89</v>
+        <v>1.35</v>
       </c>
       <c r="W85" t="n">
-        <v>4.85</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="86">
@@ -7391,31 +7391,31 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="P86" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="Q86" t="n">
         <v>0.78</v>
       </c>
       <c r="R86" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S86" t="n">
-        <v>0.659</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>7.73</v>
+        <v>5.61</v>
       </c>
       <c r="V86" t="n">
-        <v>1.47</v>
+        <v>1.07</v>
       </c>
       <c r="W86" t="n">
-        <v>7.88</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="87">
@@ -7472,31 +7472,31 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="P87" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S87" t="n">
-        <v>0.7195</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>7.31</v>
+        <v>5.19</v>
       </c>
       <c r="V87" t="n">
-        <v>1.39</v>
+        <v>0.99</v>
       </c>
       <c r="W87" t="n">
-        <v>7.45</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="88">
@@ -7553,31 +7553,31 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="P88" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="Q88" t="n">
         <v>0.78</v>
       </c>
       <c r="R88" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="S88" t="n">
-        <v>0.701</v>
+        <v>0.794</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>6.88</v>
+        <v>4.76</v>
       </c>
       <c r="V88" t="n">
-        <v>1.31</v>
+        <v>0.91</v>
       </c>
       <c r="W88" t="n">
-        <v>7.02</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="89">
@@ -7634,31 +7634,31 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="P89" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="S89" t="n">
-        <v>0.6415</v>
+        <v>0.546</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>2.27</v>
+        <v>4.76</v>
       </c>
       <c r="V89" t="n">
-        <v>0.43</v>
+        <v>0.9</v>
       </c>
       <c r="W89" t="n">
-        <v>2.36</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="90">
@@ -7715,31 +7715,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="P90" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="Q90" t="n">
         <v>0.29</v>
       </c>
       <c r="R90" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S90" t="n">
-        <v>0.718</v>
+        <v>0.6165</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>2.96</v>
+        <v>5.45</v>
       </c>
       <c r="V90" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="W90" t="n">
-        <v>3.08</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="91">
@@ -7796,31 +7796,31 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="P91" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="Q91" t="n">
         <v>0.61</v>
       </c>
       <c r="R91" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S91" t="n">
-        <v>0.753</v>
+        <v>0.645</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>3.65</v>
+        <v>6.13</v>
       </c>
       <c r="V91" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="W91" t="n">
-        <v>3.79</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="92">
@@ -7877,31 +7877,31 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="P92" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S92" t="n">
-        <v>0.5315</v>
+        <v>0.5685</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>11.83</v>
+        <v>9.69</v>
       </c>
       <c r="V92" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="W92" t="n">
-        <v>12.06</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -7958,31 +7958,31 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="P93" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="Q93" t="n">
         <v>0.76</v>
       </c>
       <c r="R93" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S93" t="n">
-        <v>0.516</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>11.02</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="V93" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="W93" t="n">
-        <v>11.23</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -8039,31 +8039,31 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="P94" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="Q94" t="n">
         <v>0.45</v>
       </c>
       <c r="R94" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S94" t="n">
-        <v>0.4865</v>
+        <v>0.543</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
       </c>
       <c r="U94" t="n">
-        <v>10.2</v>
+        <v>8.07</v>
       </c>
       <c r="V94" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="W94" t="n">
-        <v>10.4</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="95">
@@ -8120,31 +8120,31 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="P95" t="n">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="S95" t="n">
-        <v>0.4825</v>
+        <v>0.3415</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>5.96</v>
+        <v>8.81</v>
       </c>
       <c r="V95" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="W95" t="n">
-        <v>6.21</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="96">
@@ -8201,31 +8201,31 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="P96" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="Q96" t="n">
         <v>0.41</v>
       </c>
       <c r="R96" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="S96" t="n">
-        <v>0.569</v>
+        <v>0.413</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>7.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="V96" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="W96" t="n">
-        <v>7.3</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="97">
@@ -8282,31 +8282,31 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="P97" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="Q97" t="n">
         <v>0.78</v>
       </c>
       <c r="R97" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="S97" t="n">
-        <v>0.6005</v>
+        <v>0.414</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>8.07</v>
+        <v>10.91</v>
       </c>
       <c r="V97" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="W97" t="n">
-        <v>8.4</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="98">
@@ -8363,31 +8363,31 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="P98" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="Q98" t="n">
         <v>0.7</v>
       </c>
       <c r="R98" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S98" t="n">
-        <v>0.6185</v>
+        <v>0.665</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>8.35</v>
+        <v>6.77</v>
       </c>
       <c r="V98" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="W98" t="n">
-        <v>8.15</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="99">
@@ -8444,31 +8444,31 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="P99" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q99" t="n">
         <v>0.93</v>
       </c>
       <c r="R99" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S99" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
       </c>
       <c r="U99" t="n">
-        <v>7.78</v>
+        <v>6.2</v>
       </c>
       <c r="V99" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="W99" t="n">
-        <v>7.59</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="100">
@@ -8525,31 +8525,31 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="P100" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="Q100" t="n">
         <v>0.86</v>
       </c>
       <c r="R100" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="S100" t="n">
-        <v>0.7005</v>
+        <v>0.7565</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>7.21</v>
+        <v>5.62</v>
       </c>
       <c r="V100" t="n">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="W100" t="n">
-        <v>7.03</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="101">
@@ -8606,31 +8606,31 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="Q101" t="n">
         <v>0.41</v>
       </c>
       <c r="R101" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="S101" t="n">
-        <v>0.849</v>
+        <v>0.8075</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>0.24</v>
+        <v>2.83</v>
       </c>
       <c r="V101" t="n">
-        <v>0.05</v>
+        <v>0.54</v>
       </c>
       <c r="W101" t="n">
-        <v>0.23</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="102">
@@ -8687,31 +8687,31 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q102" t="n">
         <v>0.7</v>
       </c>
       <c r="R102" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="S102" t="n">
-        <v>0.907</v>
+        <v>0.836</v>
       </c>
       <c r="T102" t="n">
         <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>0.84</v>
+        <v>3.43</v>
       </c>
       <c r="V102" t="n">
-        <v>0.16</v>
+        <v>0.65</v>
       </c>
       <c r="W102" t="n">
-        <v>0.82</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="103">
@@ -8768,31 +8768,31 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="P103" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Q103" t="n">
         <v>0.93</v>
       </c>
       <c r="R103" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="S103" t="n">
-        <v>0.9155</v>
+        <v>0.8365</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>1.43</v>
+        <v>4.02</v>
       </c>
       <c r="V103" t="n">
-        <v>0.27</v>
+        <v>0.76</v>
       </c>
       <c r="W103" t="n">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="104">
@@ -8849,31 +8849,31 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P104" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q104" t="n">
         <v>0.86</v>
       </c>
       <c r="R104" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="S104" t="n">
-        <v>0.8225</v>
+        <v>0.9135</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="V104" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="W104" t="n">
-        <v>4.23</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="105">
@@ -8930,31 +8930,31 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="P105" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="S105" t="n">
-        <v>0.857</v>
+        <v>0.948</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>4.17</v>
+        <v>2.74</v>
       </c>
       <c r="V105" t="n">
-        <v>0.79</v>
+        <v>0.52</v>
       </c>
       <c r="W105" t="n">
-        <v>4.07</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="106">
@@ -9011,31 +9011,31 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="P106" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="Q106" t="n">
         <v>0.78</v>
       </c>
       <c r="R106" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="S106" t="n">
-        <v>0.8275</v>
+        <v>0.9215</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>
       </c>
       <c r="U106" t="n">
-        <v>3.94</v>
+        <v>2.51</v>
       </c>
       <c r="V106" t="n">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="W106" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
     </row>
   </sheetData>
